--- a/aula12/Alunos.xlsx
+++ b/aula12/Alunos.xlsx
@@ -436,14 +436,14 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Gustavo</t>
+          <t>Jonas</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="C2" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
     </row>
   </sheetData>
